--- a/public/templates/format-upload-tutor.xlsx
+++ b/public/templates/format-upload-tutor.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Egi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\PLCS\1PAND\PKBM\E-learning\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -44,6 +44,9 @@
     <t>Agama</t>
   </si>
   <si>
+    <t>Pendidikan Terakhir</t>
+  </si>
+  <si>
     <t>Alamat</t>
   </si>
   <si>
@@ -59,6 +62,9 @@
     <t>Kecamatan</t>
   </si>
   <si>
+    <t>Kabupaten/ Kota</t>
+  </si>
+  <si>
     <t>Provinsi</t>
   </si>
   <si>
@@ -74,10 +80,22 @@
     <t>No. SK Pengangkatan Awal</t>
   </si>
   <si>
+    <t>Lembaga Pengangkat</t>
+  </si>
+  <si>
     <t>No. SK Penugasan Terakhir</t>
   </si>
   <si>
+    <t>Lembaga Penugas</t>
+  </si>
+  <si>
     <t>TMT Kerja</t>
+  </si>
+  <si>
+    <t>Program</t>
+  </si>
+  <si>
+    <t>Kelas (Wali Kelas)</t>
   </si>
 </sst>
 </file>
@@ -462,26 +480,30 @@
     <col min="1" max="1" width="3.570313" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.710938" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.425781" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.710938" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.425781" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.14063" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.710938" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.425781" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.425781" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.570313" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.85547" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.855469" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.710938" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.14063" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21" customWidth="1"/>
-    <col min="19" max="19" width="18.85547" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.71094" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.71094" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.855469" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.710938" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.85547" customWidth="1"/>
+    <col min="22" max="22" width="15.14063" customWidth="1"/>
+    <col min="23" max="23" width="12.14063" customWidth="1"/>
+    <col min="26" max="26" width="6.710938" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5">
+    <row r="1" ht="47.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,6 +563,24 @@
       </c>
       <c r="T1" s="2" t="s">
         <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -564,6 +604,12 @@
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
     </row>
   </sheetData>
 </worksheet>

--- a/public/templates/format-upload-tutor.xlsx
+++ b/public/templates/format-upload-tutor.xlsx
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>E-Mail</t>
+  </si>
+  <si>
+    <t>Password</t>
   </si>
   <si>
     <t>Status Kepegawaian</t>
@@ -495,12 +498,14 @@
     <col min="16" max="16" width="8.855469" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.710938" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.28516" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.85547" customWidth="1"/>
+    <col min="21" max="21" width="15.42578" customWidth="1"/>
     <col min="22" max="22" width="15.14063" customWidth="1"/>
     <col min="23" max="23" width="12.14063" customWidth="1"/>
-    <col min="26" max="26" width="6.710938" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.855469" customWidth="1"/>
+    <col min="25" max="25" width="9.140625"/>
+    <col min="26" max="26" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="47.25">
@@ -581,6 +586,9 @@
       </c>
       <c r="Z1" s="2" t="s">
         <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -610,6 +618,7 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
     </row>
   </sheetData>
 </worksheet>
